--- a/output/tables/df_ports_BEST_G_TC_stats.xlsx
+++ b/output/tables/df_ports_BEST_G_TC_stats.xlsx
@@ -606,25 +606,25 @@
         <v>0.7888993452221664</v>
       </c>
       <c r="K2" t="n">
-        <v>15.31841711932986</v>
+        <v>15.31841711932985</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2050075327655099</v>
+        <v>0.2050075327655101</v>
       </c>
       <c r="M2" t="n">
-        <v>2.66104835610867</v>
+        <v>2.661048356108674</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4759160304229869</v>
+        <v>0.4759160304229876</v>
       </c>
       <c r="O2" t="n">
-        <v>5.896433848271119</v>
+        <v>5.896433848271127</v>
       </c>
       <c r="P2" t="n">
         <v>-0.1654238323643759</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.68986561483836</v>
+        <v>-2.689865614838359</v>
       </c>
       <c r="R2" t="n">
         <v>0.6226261924340035</v>
@@ -705,34 +705,34 @@
         <v>0.1169573586926704</v>
       </c>
       <c r="I3" t="n">
-        <v>4.746649516992666</v>
+        <v>4.746649516992664</v>
       </c>
       <c r="J3" t="n">
         <v>0.7859232309686279</v>
       </c>
       <c r="K3" t="n">
-        <v>15.29677294898078</v>
+        <v>15.29677294898077</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2091737112758189</v>
+        <v>0.2091737112758191</v>
       </c>
       <c r="M3" t="n">
-        <v>2.700514691978571</v>
+        <v>2.700514691978574</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4754339074993205</v>
+        <v>0.4754339074993211</v>
       </c>
       <c r="O3" t="n">
-        <v>5.926012549533326</v>
+        <v>5.926012549533331</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1634977148894132</v>
+        <v>-0.1634977148894131</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.689362752009022</v>
+        <v>-2.689362752009017</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6209528162453047</v>
+        <v>0.6209528162453049</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -810,31 +810,31 @@
         <v>0.1092288849121773</v>
       </c>
       <c r="I4" t="n">
-        <v>4.438278027105526</v>
+        <v>4.438278027105525</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7856781853489738</v>
+        <v>0.7856781853489736</v>
       </c>
       <c r="K4" t="n">
         <v>15.32613148295145</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2100537808431737</v>
+        <v>0.2100537808431739</v>
       </c>
       <c r="M4" t="n">
-        <v>2.718656055547172</v>
+        <v>2.718656055547175</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4743319723553842</v>
+        <v>0.4743319723553848</v>
       </c>
       <c r="O4" t="n">
-        <v>5.927132978254252</v>
+        <v>5.927132978254258</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.164733259636285</v>
+        <v>-0.1647332596362849</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.729245077849123</v>
+        <v>-2.729245077849118</v>
       </c>
       <c r="R4" t="n">
         <v>0.6213023280017358</v>
@@ -912,34 +912,34 @@
         <v>0.9643608477548075</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1413804818162857</v>
+        <v>0.1413804818162856</v>
       </c>
       <c r="I5" t="n">
-        <v>5.908868135905202</v>
+        <v>5.9088681359052</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4541489049192504</v>
+        <v>0.4541489049192503</v>
       </c>
       <c r="K5" t="n">
-        <v>9.454876743881755</v>
+        <v>9.45487674388175</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0641491636560588</v>
+        <v>0.06414916365605902</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9250072494648279</v>
+        <v>0.9250072494648313</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3666737941068408</v>
+        <v>0.3666737941068412</v>
       </c>
       <c r="O5" t="n">
-        <v>4.804114981425952</v>
+        <v>4.804114981425957</v>
       </c>
       <c r="P5" t="n">
         <v>-0.1213167246682341</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.068898524118746</v>
+        <v>-2.068898524118747</v>
       </c>
       <c r="R5" t="n">
         <v>0.3879335722093441</v>
@@ -1020,31 +1020,31 @@
         <v>0.118026185165393</v>
       </c>
       <c r="I6" t="n">
-        <v>4.941358889152037</v>
+        <v>4.941358889152035</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4514042675795885</v>
+        <v>0.4514042675795884</v>
       </c>
       <c r="K6" t="n">
-        <v>9.41840748584775</v>
+        <v>9.418407485847748</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06846194813366152</v>
+        <v>0.06846194813366166</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9827008227095834</v>
+        <v>0.9827008227095858</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3665411162099903</v>
+        <v>0.3665411162099906</v>
       </c>
       <c r="O6" t="n">
-        <v>4.827747058998603</v>
+        <v>4.827747058998606</v>
       </c>
       <c r="P6" t="n">
         <v>-0.1189633043708004</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.057906158827559</v>
+        <v>-2.057906158827558</v>
       </c>
       <c r="R6" t="n">
         <v>0.3846644102401878</v>
@@ -1125,7 +1125,7 @@
         <v>0.1051453955312376</v>
       </c>
       <c r="I7" t="n">
-        <v>4.405931551181299</v>
+        <v>4.405931551181298</v>
       </c>
       <c r="J7" t="n">
         <v>0.4509958582134984</v>
@@ -1134,22 +1134,22 @@
         <v>9.438348342942598</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0699287307459202</v>
+        <v>0.06992873074592035</v>
       </c>
       <c r="M7" t="n">
-        <v>1.008379906495284</v>
+        <v>1.008379906495287</v>
       </c>
       <c r="N7" t="n">
-        <v>0.364704557636765</v>
+        <v>0.3647045576367655</v>
       </c>
       <c r="O7" t="n">
-        <v>4.817029804992956</v>
+        <v>4.817029804992959</v>
       </c>
       <c r="P7" t="n">
         <v>-0.1210225456155867</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.118366579309124</v>
+        <v>-2.118366579309125</v>
       </c>
       <c r="R7" t="n">
         <v>0.384835147542939</v>
@@ -1227,34 +1227,34 @@
         <v>2.788246106422154</v>
       </c>
       <c r="H8" t="n">
-        <v>0.410474402027949</v>
+        <v>0.4104744020279492</v>
       </c>
       <c r="I8" t="n">
         <v>6.39908743364318</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2597929243757444</v>
+        <v>0.259792924375744</v>
       </c>
       <c r="K8" t="n">
-        <v>2.051279231664066</v>
+        <v>2.051279231664063</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2397165948535649</v>
+        <v>-0.2397165948535646</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.379649752901663</v>
+        <v>-1.379649752901662</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6143611757622188</v>
+        <v>0.6143611757622193</v>
       </c>
       <c r="O8" t="n">
-        <v>3.134869624078841</v>
+        <v>3.134869624078842</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.211089175119606</v>
+        <v>-0.2110891751196062</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.371388932693089</v>
+        <v>-1.37138893269309</v>
       </c>
       <c r="R8" t="n">
         <v>0.1000752787213028</v>
@@ -1332,31 +1332,31 @@
         <v>2.788246106422154</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3430319789277412</v>
+        <v>0.3430319789277413</v>
       </c>
       <c r="I9" t="n">
         <v>5.357176871475987</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2523820043373254</v>
+        <v>0.2523820043373252</v>
       </c>
       <c r="K9" t="n">
-        <v>2.002319985200463</v>
+        <v>2.00231998520046</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.2274331188817208</v>
+        <v>-0.2274331188817206</v>
       </c>
       <c r="M9" t="n">
         <v>-1.30345049497981</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6130410031260654</v>
+        <v>0.6130410031260659</v>
       </c>
       <c r="O9" t="n">
-        <v>3.145480864401485</v>
+        <v>3.145480864401486</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2040526458643821</v>
+        <v>-0.2040526458643822</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.345371442690972</v>
@@ -1443,31 +1443,31 @@
         <v>4.557070222017861</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2507483668729673</v>
+        <v>0.250748366872967</v>
       </c>
       <c r="K10" t="n">
-        <v>1.995773882928849</v>
+        <v>1.995773882928846</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.2215659884326877</v>
+        <v>-0.2215659884326875</v>
       </c>
       <c r="M10" t="n">
         <v>-1.267825474009309</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6056947688331631</v>
+        <v>0.6056947688331638</v>
       </c>
       <c r="O10" t="n">
-        <v>3.126813700235314</v>
+        <v>3.126813700235317</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2122896108435292</v>
+        <v>-0.2122896108435295</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.423040140734475</v>
+        <v>-1.423040140734477</v>
       </c>
       <c r="R10" t="n">
-        <v>0.09652765302205124</v>
+        <v>0.09652765302205102</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
